--- a/excel_automation/project/Employee Sales.xlsx
+++ b/excel_automation/project/Employee Sales.xlsx
@@ -1,149 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LearningCourses\ZeroToMastery\ztm-the-python-automation-bootcamp\excel_automation\project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8FA4D3-EC20-4D18-918D-FF84E6FC39E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Dataset 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Dataset 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dataset 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diffs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Q1 Sales</t>
-  </si>
-  <si>
-    <t>Q2 Sales</t>
-  </si>
-  <si>
-    <t>Q3 Sales</t>
-  </si>
-  <si>
-    <t>Q4 Sales</t>
-  </si>
-  <si>
-    <t>Amari Copeland</t>
-  </si>
-  <si>
-    <t>Elisabeth Kennedy</t>
-  </si>
-  <si>
-    <t>Kadyn Madden</t>
-  </si>
-  <si>
-    <t>Niko Gomez</t>
-  </si>
-  <si>
-    <t>Jazmine Liu</t>
-  </si>
-  <si>
-    <t>Leila Rollins</t>
-  </si>
-  <si>
-    <t>Luciana Ball</t>
-  </si>
-  <si>
-    <t>Remington Maynard</t>
-  </si>
-  <si>
-    <t>Teresa Frost</t>
-  </si>
-  <si>
-    <t>Logan Dickerson</t>
-  </si>
-  <si>
-    <t>Jakayla Hopkins</t>
-  </si>
-  <si>
-    <t>Leticia Tyler</t>
-  </si>
-  <si>
-    <t>Charity Logan</t>
-  </si>
-  <si>
-    <t>Meadow Berg</t>
-  </si>
-  <si>
-    <t>Penelope Alexander</t>
-  </si>
-  <si>
-    <t>Ada Mccann</t>
-  </si>
-  <si>
-    <t>Ivan Brennan</t>
-  </si>
-  <si>
-    <t>Penelope Stephens</t>
-  </si>
-  <si>
-    <t>Giana Villarreal</t>
-  </si>
-  <si>
-    <t>Ian Bean</t>
-  </si>
-  <si>
-    <t>Kadyn Maden</t>
-  </si>
-  <si>
-    <t>Jasmine Liu</t>
-  </si>
-  <si>
-    <t>Remington Maynerd</t>
-  </si>
-  <si>
-    <t>Ivan Brennen</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -161,23 +55,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -378,372 +332,423 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="5" width="15.453125" customWidth="1"/>
-    <col min="6" max="26" width="12.90625" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15.453125" customWidth="1" min="2" max="5"/>
+    <col width="12.90625" customWidth="1" min="6" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Q1 Sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q2 Sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 Sales</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Amari Copeland</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>157011</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>264813</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="n">
         <v>362024</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="n">
         <v>289476</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elisabeth Kennedy</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>149160</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>155046</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="1" t="n">
         <v>155730</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="n">
         <v>228380</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Kadyn Madden</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>328166</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>108331</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="n">
         <v>253512</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="n">
         <v>316376</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Niko Gomez</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>292603</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>291312</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="n">
         <v>236326</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1" t="n">
         <v>324481</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Jazmine Liu</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>200587</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>274313</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="n">
         <v>286772</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="n">
         <v>140940</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Leila Rollins</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>239367</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>164813</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="n">
         <v>139468</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="n">
         <v>298890</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Luciana Ball</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>304546</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>284811</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="n">
         <v>101415</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="n">
         <v>179600</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Remington Maynard</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>187510</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>184079</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="n">
         <v>313757</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1" t="n">
         <v>313899</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Teresa Frost</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>145889</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="1" t="n">
         <v>345268</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="n">
         <v>145058</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1" t="n">
         <v>110824</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Logan Dickerson</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>352920</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="n">
         <v>367737</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="1" t="n">
         <v>188663</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="n">
         <v>119595</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Jakayla Hopkins</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>108904</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="n">
         <v>225087</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="1" t="n">
         <v>248226</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1" t="n">
         <v>162736</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Leticia Tyler</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>298366</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="n">
         <v>230501</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="1" t="n">
         <v>350850</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="n">
         <v>265264</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Charity Logan</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>384519</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="1" t="n">
         <v>259513</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="1" t="n">
         <v>381093</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="n">
         <v>317324</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Meadow Berg</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>307453</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="1" t="n">
         <v>229295</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="1" t="n">
         <v>170808</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="n">
         <v>121559</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Penelope Alexander</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>229940</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="1" t="n">
         <v>171281</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="1" t="n">
         <v>307894</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1" t="n">
         <v>257516</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ada Mccann</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>299326</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="1" t="n">
         <v>368328</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="1" t="n">
         <v>201837</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1" t="n">
         <v>215489</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ivan Brennan</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>187810</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="1" t="n">
         <v>359492</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="1" t="n">
         <v>213408</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1" t="n">
         <v>321427</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Penelope Stephens</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>236865</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="1" t="n">
         <v>336889</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="1" t="n">
         <v>120582</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1" t="n">
         <v>341707</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Giana Villarreal</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>312479</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="1" t="n">
         <v>237258</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="1" t="n">
         <v>125608</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1" t="n">
         <v>382063</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ian Bean</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>370769</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="1" t="n">
         <v>128327</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="1" t="n">
         <v>361262</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1" t="n">
         <v>215052</v>
       </c>
     </row>
@@ -753,375 +758,662 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="5" width="15.453125" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15.453125" customWidth="1" min="2" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Q1 Sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q2 Sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 Sales</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Amari Copeland</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>157011</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>264813</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="n">
         <v>362024</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="n">
         <v>289476</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elisabeth Kennedy</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>149160</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>155046</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="1" t="n">
         <v>155730</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="n">
         <v>228380</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Kadyn Maden</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>309434</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>108331</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="n">
         <v>253512</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="n">
         <v>316376</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Niko Gomez</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>292603</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>291312</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="n">
         <v>236326</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1" t="n">
         <v>324481</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Jasmine Liu</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>200587</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>274313</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="n">
         <v>286772</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="n">
         <v>140940</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Leila Rollins</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>239367</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>164813</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="n">
         <v>139468</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="n">
         <v>298890</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Luciana Ball</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>304546</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>284811</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="n">
         <v>101415</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="n">
         <v>229123</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Remington Maynerd</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>187510</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>184079</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="n">
         <v>313757</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1" t="n">
         <v>313899</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Teresa Frost</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>145889</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="1" t="n">
         <v>345268</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="n">
         <v>145058</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1" t="n">
         <v>89163</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Logan Dickerson</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>352920</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="n">
         <v>367737</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="1" t="n">
         <v>188663</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="n">
         <v>119595</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Jakayla Hopkins</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>108904</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="n">
         <v>176103</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="1" t="n">
         <v>215604</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1" t="n">
         <v>162736</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Leticia Tyler</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>298366</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="n">
         <v>230501</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="1" t="n">
         <v>350850</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="n">
         <v>265264</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Charity Logan</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>384519</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="1" t="n">
         <v>259513</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="1" t="n">
         <v>381093</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="n">
         <v>317324</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Meadow Berg</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>307453</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="1" t="n">
         <v>229295</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="1" t="n">
         <v>170808</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="n">
         <v>121559</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Penelope Alexander</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>229940</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="1" t="n">
         <v>171281</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="1" t="n">
         <v>307894</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1" t="n">
         <v>257516</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ada Mccann</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>299326</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="1" t="n">
         <v>368328</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="1" t="n">
         <v>201837</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1" t="n">
         <v>215489</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ivan Brennen</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>187810</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="1" t="n">
         <v>359492</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="1" t="n">
         <v>213408</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1" t="n">
         <v>321427</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Penelope Stephens</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>236865</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="1" t="n">
         <v>336889</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="1" t="n">
         <v>120582</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1" t="n">
         <v>361728</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Giana Villarreal</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>312479</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="1" t="n">
         <v>237258</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="1" t="n">
         <v>125608</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1" t="n">
         <v>382063</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ian Bean</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>370769</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="1" t="n">
         <v>128327</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="1" t="n">
         <v>361262</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1" t="n">
         <v>215052</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Value 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Value 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kadyn Madden</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kadyn Maden</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Q1 Sales</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>328166</v>
+      </c>
+      <c r="D3" t="n">
+        <v>309434</v>
+      </c>
+      <c r="E3" s="2">
+        <f>ABS(C3-D3)/AVERAGE(C3:D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jazmine Liu</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jasmine Liu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Q4 Sales</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>179600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>229123</v>
+      </c>
+      <c r="E5" s="2">
+        <f>ABS(C5-D5)/AVERAGE(C5:D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remington Maynard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Remington Maynerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Q4 Sales</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>110824</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89163</v>
+      </c>
+      <c r="E7" s="2">
+        <f>ABS(C7-D7)/AVERAGE(C7:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q2 Sales</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>225087</v>
+      </c>
+      <c r="D8" t="n">
+        <v>176103</v>
+      </c>
+      <c r="E8" s="2">
+        <f>ABS(C8-D8)/AVERAGE(C8:D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Q3 Sales</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>248226</v>
+      </c>
+      <c r="D9" t="n">
+        <v>215604</v>
+      </c>
+      <c r="E9" s="2">
+        <f>ABS(C9-D9)/AVERAGE(C9:D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ivan Brennan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ivan Brennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Q4 Sales</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>341707</v>
+      </c>
+      <c r="D11" t="n">
+        <v>361728</v>
+      </c>
+      <c r="E11" s="2">
+        <f>ABS(C11-D11)/AVERAGE(C11:D11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>